--- a/all_sim/det_gpt_domain.xlsx
+++ b/all_sim/det_gpt_domain.xlsx
@@ -332,15 +332,15 @@
   <cols>
     <col width="34.1" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="23.1" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="8" max="8" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.5979052823315119</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.19022817460317462</v>
+        <v>0.486780753968254</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.32</v>
+        <v>0.5565517241379311</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.32</v>
+        <v>0.5565517241379311</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.32</v>
+        <v>0.5565517241379311</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.32</v>
+        <v>0.5565517241379311</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.32</v>
+        <v>0.5565517241379311</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.32</v>
+        <v>0.5565517241379311</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.32</v>
+        <v>0.5565517241379311</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.32</v>
+        <v>0.5565517241379311</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.7100614439324117</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.6673669467787114</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.6949404761904762</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.6949404761904762</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.6949404761904762</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.6949404761904762</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.6949404761904762</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.6949404761904762</v>
       </c>
     </row>
     <row r="3">
@@ -436,22 +436,22 @@
         <v>1.0</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.75</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.6930434782608695</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.2545454545454545</v>
+        <v>0.5022727272727272</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.05292929292929294</v>
+        <v>0.36674242424242426</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.3472222222222222</v>
+        <v>0.5805878552971576</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.625</v>
+        <v>0.8125</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.625</v>
+        <v>0.8125</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.625</v>
+        <v>0.8125</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.625</v>
+        <v>0.8125</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.625</v>
+        <v>0.8125</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.625</v>
+        <v>0.8125</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.625</v>
+        <v>0.8125</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.625</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="5">
@@ -510,22 +510,22 @@
         <v>1.0</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.9285714285714286</v>
       </c>
     </row>
     <row r="6">
@@ -535,34 +535,34 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="7">
@@ -578,28 +578,28 @@
         <v>1.0</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.5625</v>
+        <v>0.7733134920634921</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.9090909090909092</v>
       </c>
     </row>
     <row r="8">
@@ -609,262 +609,262 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9571428571428571</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8172043010752688</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8172043010752688</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8172043010752688</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8172043010752688</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8172043010752688</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.6</v>
+        <v>0.751219512195122</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.6</v>
+        <v>0.5971014492753624</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.6</v>
+        <v>0.5247706422018348</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>manufacturing_tomaskova_4</t>
+          <t>manufacturing_lodhi_5</t>
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.9864864864864865</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.40816326530612246</v>
+        <v>0.9473684210526316</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.05672799422799423</v>
+        <v>0.9473684210526316</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.07017543859649122</v>
+        <v>0.9473684210526316</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.9473684210526316</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.0683760683760684</v>
+        <v>0.9473684210526316</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.9473684210526316</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.9473684210526316</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.9473684210526316</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.053333333333333344</v>
+        <v>0.9473684210526316</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>tourism_bpmai_1</t>
+          <t>manufacturing_tomaskova_4</t>
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8436293436293436</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6374149659863946</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2540133477633478</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5078149920255184</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5070175438596491</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5074023199023199</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5070175438596491</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5063223029324724</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5063223029324724</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5042786069651741</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>tourism_corradini_2</t>
+          <t>tourism_bpmai_1</t>
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.9242063492063493</v>
+        <v>0.5637254901960784</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.9242063492063493</v>
+        <v>0.5637254901960784</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>1.0</v>
+        <v>0.5637254901960784</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>1.0</v>
+        <v>0.5637254901960784</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>1.0</v>
+        <v>0.5637254901960784</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.5637254901960784</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.5637254901960784</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.9492063492063492</v>
+        <v>0.5637254901960784</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.9092063492063491</v>
+        <v>0.5637254901960784</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.9092063492063491</v>
+        <v>0.5637254901960784</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>tourism_fouad_3</t>
+          <t>tourism_corradini_2</t>
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9492826617826617</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9492826617826617</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9634146341463414</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9634146341463414</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.9270833333333334</v>
+        <v>0.9634146341463414</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.9270833333333334</v>
+        <v>0.9523035230352304</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.9270833333333334</v>
+        <v>0.9760683760683762</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.9270833333333334</v>
+        <v>0.9246031746031746</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.9270833333333334</v>
+        <v>0.9046031746031746</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.9270833333333334</v>
+        <v>0.9046031746031746</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>tourism_web_5</t>
+          <t>tourism_fouad_3</t>
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.9255514705882353</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.904718137254902</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.904718137254902</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.904718137254902</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.904718137254902</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.904718137254902</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.904718137254902</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>gdpr_4_right_of_portability</t>
+          <t>tourism_web_5</t>
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>1</v>
+        <v>0.9613095238095238</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>1</v>
+        <v>0.9613095238095238</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>1</v>
+        <v>0.9613095238095238</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>1</v>
+        <v>0.9613095238095238</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>1</v>
+        <v>0.9613095238095238</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>1</v>
+        <v>0.9613095238095238</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>1</v>
+        <v>0.9613095238095238</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>1</v>
+        <v>0.9613095238095238</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>1</v>
+        <v>0.9613095238095238</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>1</v>
+        <v>0.9613095238095238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>gdpr_7_right_to_be_forgotten</t>
+          <t>gdpr_4_right_of_portability</t>
         </is>
       </c>
       <c r="B15" s="0" t="n">
@@ -901,7 +901,7 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t>healthcare_redeker_5</t>
+          <t>gdpr_7_right_to_be_forgotten</t>
         </is>
       </c>
       <c r="B16" s="0" t="n">
@@ -938,7 +938,7 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>logistics_cimino_3</t>
+          <t>healthcare_redeker_5</t>
         </is>
       </c>
       <c r="B17" s="0" t="n">
@@ -975,7 +975,7 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t>logistics_klessascheck_5</t>
+          <t>logistics_cimino_3</t>
         </is>
       </c>
       <c r="B18" s="0" t="n">
@@ -1012,7 +1012,7 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>logistics_signavio_2</t>
+          <t>logistics_klessascheck_5</t>
         </is>
       </c>
       <c r="B19" s="0" t="n">
@@ -1049,7 +1049,7 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t>manufacturing_bpmai_1</t>
+          <t>logistics_signavio_2</t>
         </is>
       </c>
       <c r="B20" s="0" t="n">
@@ -1086,7 +1086,7 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>manufacturing_bpmai_2</t>
+          <t>manufacturing_bpmai_1</t>
         </is>
       </c>
       <c r="B21" s="0" t="n">
@@ -1123,7 +1123,7 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>manufacturing_lodhi_5</t>
+          <t>manufacturing_bpmai_2</t>
         </is>
       </c>
       <c r="B22" s="0" t="n">

--- a/all_sim/det_gpt_domain.xlsx
+++ b/all_sim/det_gpt_domain.xlsx
@@ -332,15 +332,15 @@
   <cols>
     <col width="34.1" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.5979052823315119</v>
+        <v>0.2550091074681239</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.486780753968254</v>
+        <v>0.14901207010582013</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.5565517241379311</v>
+        <v>0.2537931034482759</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.5565517241379311</v>
+        <v>0.2537931034482759</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.5565517241379311</v>
+        <v>0.2537931034482759</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.5565517241379311</v>
+        <v>0.2537931034482759</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.5565517241379311</v>
+        <v>0.2537931034482759</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.5565517241379311</v>
+        <v>0.2537931034482759</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.5565517241379311</v>
+        <v>0.2537931034482759</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.5565517241379311</v>
+        <v>0.2537931034482759</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.7100614439324117</v>
+        <v>0.4377880184331797</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.6673669467787114</v>
+        <v>0.3991596638655462</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.6949404761904762</v>
+        <v>0.42410714285714285</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.6949404761904762</v>
+        <v>0.42410714285714285</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.6949404761904762</v>
+        <v>0.42410714285714285</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.6949404761904762</v>
+        <v>0.42410714285714285</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.6949404761904762</v>
+        <v>0.42410714285714285</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.6949404761904762</v>
+        <v>0.42410714285714285</v>
       </c>
     </row>
     <row r="3">
@@ -436,22 +436,22 @@
         <v>1.0</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6875</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.6930434782608695</v>
+        <v>0.4626086956521739</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.5022727272727272</v>
+        <v>0.1909090909090909</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.36674242424242426</v>
+        <v>0.03602132435465769</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.5805878552971576</v>
+        <v>0.2826227390180878</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.32407407407407407</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="5">
@@ -510,22 +510,22 @@
         <v>1.0</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.8571428571428572</v>
       </c>
     </row>
     <row r="6">
@@ -535,34 +535,34 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
     </row>
     <row r="7">
@@ -578,28 +578,28 @@
         <v>1.0</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.7733134920634921</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.9571428571428571</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.8172043010752688</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.8172043010752688</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.8172043010752688</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.8172043010752688</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.8172043010752688</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.751219512195122</v>
+        <v>0.5414634146341464</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.5971014492753624</v>
+        <v>0.3565217391304348</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.5247706422018348</v>
+        <v>0.2697247706422018</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.9864864864864865</v>
+        <v>0.972972972972973</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.9473684210526316</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.9473684210526316</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.9473684210526316</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.9473684210526316</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.9473684210526316</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.9473684210526316</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.9473684210526316</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.9473684210526316</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.9473684210526316</v>
+        <v>0.8947368421052632</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.8436293436293436</v>
+        <v>0.694980694980695</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.6374149659863946</v>
+        <v>0.35374149659863946</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.2540133477633478</v>
+        <v>0.02560127012237402</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.5078149920255184</v>
+        <v>0.06634768740031897</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.5070175438596491</v>
+        <v>0.0631578947368421</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.5074023199023199</v>
+        <v>0.06471306471306473</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.5070175438596491</v>
+        <v>0.0631578947368421</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.5063223029324724</v>
+        <v>0.060263653483992465</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.5063223029324724</v>
+        <v>0.060263653483992465</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.5042786069651741</v>
+        <v>0.05094527363184081</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.5637254901960784</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.5637254901960784</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.5637254901960784</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.5637254901960784</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.5637254901960784</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.5637254901960784</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.5637254901960784</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.5637254901960784</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.5637254901960784</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.5637254901960784</v>
+        <v>0.2647058823529412</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.9492826617826617</v>
+        <v>0.9005087505087506</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.9492826617826617</v>
+        <v>0.9005087505087506</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.9634146341463414</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.9634146341463414</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.9634146341463414</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.9523035230352304</v>
+        <v>0.9062330623306234</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.9760683760683762</v>
+        <v>0.9527065527065528</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.9246031746031746</v>
+        <v>0.8542857142857143</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.9046031746031746</v>
+        <v>0.8182857142857143</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.9046031746031746</v>
+        <v>0.8182857142857143</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.904718137254902</v>
+        <v>0.8180147058823529</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.904718137254902</v>
+        <v>0.8180147058823529</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.904718137254902</v>
+        <v>0.8180147058823529</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.904718137254902</v>
+        <v>0.8180147058823529</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.904718137254902</v>
+        <v>0.8180147058823529</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.904718137254902</v>
+        <v>0.8180147058823529</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
     </row>
     <row r="15">
